--- a/Listing/SNK06D.xlsx
+++ b/Listing/SNK06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1416" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1434" uniqueCount="525">
   <si>
     <t/>
   </si>
@@ -127,36 +127,30 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20138227</t>
-  </si>
-  <si>
-    <t>LAYS WAVYAYM GRG 64G</t>
-  </si>
-  <si>
-    <t>20138226</t>
-  </si>
-  <si>
-    <t>LAYS PDS MANIS 64G</t>
-  </si>
-  <si>
     <t>20138229</t>
   </si>
   <si>
     <t>LAYS DGG SAPI BKR64G</t>
   </si>
   <si>
+    <t>20141504</t>
+  </si>
+  <si>
+    <t>LAYS RMPT LAUT PDS64</t>
+  </si>
+  <si>
+    <t>20132750</t>
+  </si>
+  <si>
+    <t>CHITATO AYAM BWG 65G</t>
+  </si>
+  <si>
     <t>20131037</t>
   </si>
   <si>
     <t>CHTATOLITE ABR.SWD65</t>
   </si>
   <si>
-    <t>20116679</t>
-  </si>
-  <si>
-    <t>CHTATO LITE BBQ 65G</t>
-  </si>
-  <si>
     <t>20116670</t>
   </si>
   <si>
@@ -169,12 +163,6 @@
     <t>CHTATO LITE SLMON 68</t>
   </si>
   <si>
-    <t>20132750</t>
-  </si>
-  <si>
-    <t>CHITATO AYAM BWG 65G</t>
-  </si>
-  <si>
     <t>20116686</t>
   </si>
   <si>
@@ -259,28 +247,37 @@
     <t>MR.POTATO GHOST/P 40</t>
   </si>
   <si>
+    <t>20120198</t>
+  </si>
+  <si>
+    <t>MR/P GHST/P SWEED40</t>
+  </si>
+  <si>
     <t>20120199</t>
   </si>
   <si>
     <t>MR/P GHST/P CHEESE40</t>
   </si>
   <si>
-    <t>20120198</t>
-  </si>
-  <si>
-    <t>MR/P GHST/P SWEED40</t>
-  </si>
-  <si>
     <t>7</t>
   </si>
   <si>
+    <t>20141098</t>
+  </si>
+  <si>
+    <t>MR PTT BULDAK CHES40</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>20139841</t>
   </si>
   <si>
     <t>MR POTATO CRBNARA 40</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
@@ -292,7 +289,7 @@
     <t>LAYS STAX SOUR&amp;O 70G</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>20139536</t>
@@ -301,7 +298,7 @@
     <t>LAYS STAX ORGNL 70G</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>20023846</t>
@@ -322,22 +319,31 @@
     <t>PRNGLES S.CRM&amp;O 102G</t>
   </si>
   <si>
+    <t>20141457</t>
+  </si>
+  <si>
+    <t>PRLGS BR SWD 102</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
     <t>20136007</t>
   </si>
   <si>
-    <t>MR.POTATO BBQ 106G</t>
+    <t>MR.POTATO BBQ 85G</t>
   </si>
   <si>
     <t>20135539</t>
   </si>
   <si>
-    <t>MR.POTATO ORGNL 106G</t>
+    <t>MR.POTATO ORGINAL85G</t>
   </si>
   <si>
     <t>20135538</t>
   </si>
   <si>
-    <t>MR.POTATO SOUR&amp;O 106</t>
+    <t>MR.POTATO SOUR&amp;O 85G</t>
   </si>
   <si>
     <t>20137054</t>
@@ -490,9 +496,6 @@
     <t>QTELA KRPK BLDO 175G</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>20012681</t>
   </si>
   <si>
@@ -526,6 +529,12 @@
     <t>12</t>
   </si>
   <si>
+    <t>20140882</t>
+  </si>
+  <si>
+    <t>LAYS WAVY SAPI 105G</t>
+  </si>
+  <si>
     <t>20122571</t>
   </si>
   <si>
@@ -631,12 +640,6 @@
     <t>GRD O'CORN JG/BKR 70</t>
   </si>
   <si>
-    <t>20138717</t>
-  </si>
-  <si>
-    <t>CRUNCHY SM SWD 60G</t>
-  </si>
-  <si>
     <t>20139291</t>
   </si>
   <si>
@@ -802,7 +805,7 @@
     <t>20104942</t>
   </si>
   <si>
-    <t>CHIKI BALL CHOCO 55G</t>
+    <t>CHIKI BALL CHOCO 50G</t>
   </si>
   <si>
     <t>20</t>
@@ -817,13 +820,55 @@
     <t>20101064</t>
   </si>
   <si>
-    <t>CHIKI BALL CHEESE 55</t>
+    <t>CHIKI BALL CHEESE 50</t>
   </si>
   <si>
     <t>20101065</t>
   </si>
   <si>
-    <t>CHIKI BALL CHKN 55</t>
+    <t>CHIKI BALL CHKN 50</t>
+  </si>
+  <si>
+    <t>20140251</t>
+  </si>
+  <si>
+    <t>CHIKI P/C SALT CRM72</t>
+  </si>
+  <si>
+    <t>20140264</t>
+  </si>
+  <si>
+    <t>CHIKI NUTTY CRML 50G</t>
+  </si>
+  <si>
+    <t>RT,(E-15H)</t>
+  </si>
+  <si>
+    <t>20132657</t>
+  </si>
+  <si>
+    <t>WONHAE TPKI CRM.RS80</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20139930</t>
+  </si>
+  <si>
+    <t>WONHAE TPKI CHS TR80</t>
+  </si>
+  <si>
+    <t>20141100</t>
+  </si>
+  <si>
+    <t>WONHAE BANANA MB 60G</t>
+  </si>
+  <si>
+    <t>20116410</t>
+  </si>
+  <si>
+    <t>CHIKI TWIST CORN 75G</t>
   </si>
   <si>
     <t>20140272</t>
@@ -832,34 +877,31 @@
     <t>CHIKI TWIST CORN 120</t>
   </si>
   <si>
-    <t>RT,(E-15H)</t>
-  </si>
-  <si>
-    <t>20140264</t>
-  </si>
-  <si>
-    <t>CHIKI NUTTY CRML 50G</t>
-  </si>
-  <si>
     <t>20034682</t>
   </si>
   <si>
     <t>RIN-BEE STICK KEJU60</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20132657</t>
-  </si>
-  <si>
-    <t>WONHAE TPKI CRM.RS80</t>
-  </si>
-  <si>
-    <t>20139930</t>
-  </si>
-  <si>
-    <t>WONHAE TPKI CHS TR80</t>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20057730</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWNG 70</t>
+  </si>
+  <si>
+    <t>20103371</t>
+  </si>
+  <si>
+    <t>TIC TIC STK BWG+SS65</t>
+  </si>
+  <si>
+    <t>20072575</t>
+  </si>
+  <si>
+    <t>KRISBEE F.FRIES 65G</t>
   </si>
   <si>
     <t>20016624</t>
@@ -868,16 +910,208 @@
     <t>STT FRENCH FRIES 24G</t>
   </si>
   <si>
-    <t>20116410</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST CORN 75G</t>
-  </si>
-  <si>
-    <t>20129201</t>
-  </si>
-  <si>
-    <t>CHIKI TWIST F.HOT 75</t>
+    <t>20125389</t>
+  </si>
+  <si>
+    <t>STT FRCH FRS LVL3 60</t>
+  </si>
+  <si>
+    <t>20138241</t>
+  </si>
+  <si>
+    <t>CHEETOS KEJU 120G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20132876</t>
+  </si>
+  <si>
+    <t>OISHIT THIN TRUFF100</t>
+  </si>
+  <si>
+    <t>20140085</t>
+  </si>
+  <si>
+    <t>O/TATER THIN SWD 100</t>
+  </si>
+  <si>
+    <t>20024699</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 62G</t>
+  </si>
+  <si>
+    <t>20138236</t>
+  </si>
+  <si>
+    <t>CHEETOS JGG BKR 120G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20134273</t>
+  </si>
+  <si>
+    <t>POPPY POP JGG BKR130</t>
+  </si>
+  <si>
+    <t>20092858</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 145</t>
+  </si>
+  <si>
+    <t>20133064</t>
+  </si>
+  <si>
+    <t>KRAKER UDANG PDS 130</t>
+  </si>
+  <si>
+    <t>20138106</t>
+  </si>
+  <si>
+    <t>TIC TIC STCK BWG 135</t>
+  </si>
+  <si>
+    <t>20092857</t>
+  </si>
+  <si>
+    <t>STT FRENCH FRIES 130</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20119036</t>
+  </si>
+  <si>
+    <t>RIN-BEE STK KJU 130G</t>
+  </si>
+  <si>
+    <t>20126424</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 115G</t>
+  </si>
+  <si>
+    <t>20120421</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 115G</t>
+  </si>
+  <si>
+    <t>20101933</t>
+  </si>
+  <si>
+    <t>CHIKI BALL CHOC 200G</t>
+  </si>
+  <si>
+    <t>20117923</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR ORI2'S</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20022707</t>
+  </si>
+  <si>
+    <t>TAO KAE CRSPY ORG 15</t>
+  </si>
+  <si>
+    <t>20137779</t>
+  </si>
+  <si>
+    <t>TAO KAE/N WGYU 6G</t>
+  </si>
+  <si>
+    <t>20024856</t>
+  </si>
+  <si>
+    <t>TAO KAE CLASSIC 3.2G</t>
+  </si>
+  <si>
+    <t>20137577</t>
+  </si>
+  <si>
+    <t>TKN SPICY MAYO 3.2G</t>
+  </si>
+  <si>
+    <t>20072581</t>
+  </si>
+  <si>
+    <t>IDM SEAWEED ORG 20G</t>
+  </si>
+  <si>
+    <t>20072582</t>
+  </si>
+  <si>
+    <t>IDM SEAWEED BBQ 20G</t>
+  </si>
+  <si>
+    <t>20138203</t>
+  </si>
+  <si>
+    <t>M/SK GIM BORI BIG 3G</t>
+  </si>
+  <si>
+    <t>20117928</t>
+  </si>
+  <si>
+    <t>T K NOI S/LVR SPCY2S</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20042370</t>
+  </si>
+  <si>
+    <t>M/SUKA R/LAUT PNG 9G</t>
+  </si>
+  <si>
+    <t>20097390</t>
+  </si>
+  <si>
+    <t>M/SUKA NORI BBQ2X4.5</t>
+  </si>
+  <si>
+    <t>20073871</t>
+  </si>
+  <si>
+    <t>M/SUKA NORI PDS2X4.5</t>
+  </si>
+  <si>
+    <t>20097391</t>
+  </si>
+  <si>
+    <t>M/SK NORI S.EGG2X4.5</t>
+  </si>
+  <si>
+    <t>20118737</t>
+  </si>
+  <si>
+    <t>M/SK NORI J.BKR2X4.5</t>
+  </si>
+  <si>
+    <t>20064426</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 70G</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>10006890</t>
+  </si>
+  <si>
+    <t>TWISTKO JGNG BKR 40G</t>
   </si>
   <si>
     <t>20114756</t>
@@ -886,9 +1120,6 @@
     <t>GURIBEE BBQ BLDO 65G</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>20114757</t>
   </si>
   <si>
@@ -901,226 +1132,154 @@
     <t>GURIBEE KEJU 65G</t>
   </si>
   <si>
-    <t>20057730</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWNG 70</t>
-  </si>
-  <si>
-    <t>20103371</t>
-  </si>
-  <si>
-    <t>TIC TIC STK BWG+SS65</t>
-  </si>
-  <si>
-    <t>20125389</t>
-  </si>
-  <si>
-    <t>STT FRCH FRS LVL3 60</t>
-  </si>
-  <si>
-    <t>20138241</t>
-  </si>
-  <si>
-    <t>CHEETOS KEJU 120G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20132876</t>
-  </si>
-  <si>
-    <t>OISHIT THIN TRUFF100</t>
-  </si>
-  <si>
-    <t>20140085</t>
-  </si>
-  <si>
-    <t>O/TATER THIN SWD 100</t>
-  </si>
-  <si>
-    <t>20072575</t>
-  </si>
-  <si>
-    <t>KRISBEE F.FRIES 65G</t>
-  </si>
-  <si>
-    <t>20024699</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 62G</t>
-  </si>
-  <si>
-    <t>20138236</t>
-  </si>
-  <si>
-    <t>CHEETOS JGG BKR 120G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20134273</t>
-  </si>
-  <si>
-    <t>POPPY POP JGG BKR130</t>
-  </si>
-  <si>
-    <t>20092858</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 145</t>
-  </si>
-  <si>
-    <t>20133064</t>
-  </si>
-  <si>
-    <t>KRAKER UDANG PDS 130</t>
-  </si>
-  <si>
-    <t>20138106</t>
-  </si>
-  <si>
-    <t>TIC TIC STCK BWG 135</t>
-  </si>
-  <si>
-    <t>20092857</t>
-  </si>
-  <si>
-    <t>STT FRENCH FRIES 130</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20119036</t>
-  </si>
-  <si>
-    <t>RIN-BEE STK KJU 130G</t>
-  </si>
-  <si>
-    <t>20126424</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 115G</t>
-  </si>
-  <si>
-    <t>20120421</t>
-  </si>
-  <si>
-    <t>TARO POTATO BBQ 115G</t>
-  </si>
-  <si>
-    <t>20101933</t>
-  </si>
-  <si>
-    <t>CHIKI BALL CHOC 200G</t>
-  </si>
-  <si>
-    <t>20117923</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR ORI2'S</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20022707</t>
-  </si>
-  <si>
-    <t>TAO KAE CRSPY ORG 15</t>
-  </si>
-  <si>
-    <t>20137779</t>
-  </si>
-  <si>
-    <t>TAO KAE/N WGYU 6G</t>
-  </si>
-  <si>
-    <t>20024856</t>
-  </si>
-  <si>
-    <t>TAO KAE CLASSIC 3.2G</t>
-  </si>
-  <si>
-    <t>20137577</t>
-  </si>
-  <si>
-    <t>TKN SPICY MAYO 3.2G</t>
-  </si>
-  <si>
-    <t>20072581</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED ORG 20G</t>
-  </si>
-  <si>
-    <t>20072582</t>
-  </si>
-  <si>
-    <t>IDM SEAWEED BBQ 20G</t>
-  </si>
-  <si>
-    <t>20138203</t>
-  </si>
-  <si>
-    <t>M/SK GIM BORI BIG 3G</t>
-  </si>
-  <si>
-    <t>20117928</t>
-  </si>
-  <si>
-    <t>T K NOI S/LVR SPCY2S</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20042370</t>
-  </si>
-  <si>
-    <t>M/SUKA R/LAUT PNG 9G</t>
-  </si>
-  <si>
-    <t>20097390</t>
-  </si>
-  <si>
-    <t>M/SUKA NORI BBQ2X4.5</t>
-  </si>
-  <si>
-    <t>20073871</t>
-  </si>
-  <si>
-    <t>M/SUKA NORI PDS2X4.5</t>
-  </si>
-  <si>
-    <t>20097391</t>
-  </si>
-  <si>
-    <t>M/SK NORI S.EGG2X4.5</t>
-  </si>
-  <si>
-    <t>20118737</t>
-  </si>
-  <si>
-    <t>M/SK NORI J.BKR2X4.5</t>
-  </si>
-  <si>
-    <t>20064426</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 70G</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>10006890</t>
-  </si>
-  <si>
-    <t>TWISTKO JGNG BKR 40G</t>
+    <t>20138466</t>
+  </si>
+  <si>
+    <t>NABATI AHH STRW 30G</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20135812</t>
+  </si>
+  <si>
+    <t>NABATI RCHSE AHH 30G</t>
+  </si>
+  <si>
+    <t>20141505</t>
+  </si>
+  <si>
+    <t>JETZ CROISANT CHOC50</t>
+  </si>
+  <si>
+    <t>20137069</t>
+  </si>
+  <si>
+    <t>KUSUKA UBI BBQ 42G</t>
+  </si>
+  <si>
+    <t>20004229</t>
+  </si>
+  <si>
+    <t>SMAX RING CHEESE 40G</t>
+  </si>
+  <si>
+    <t>20081238</t>
+  </si>
+  <si>
+    <t>TARO NET TRYK BBQ 62</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20055205</t>
+  </si>
+  <si>
+    <t>TARO SEAWEED 62G</t>
+  </si>
+  <si>
+    <t>20055204</t>
+  </si>
+  <si>
+    <t>TARO POTATO BBQ 62G</t>
+  </si>
+  <si>
+    <t>10000753</t>
+  </si>
+  <si>
+    <t>TARO SNACK SEAWED 32</t>
+  </si>
+  <si>
+    <t>10000752</t>
+  </si>
+  <si>
+    <t>TARO SNACK BARBQ 32G</t>
+  </si>
+  <si>
+    <t>20069696</t>
+  </si>
+  <si>
+    <t>OISHI POPCRN KRML100</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20069844</t>
+  </si>
+  <si>
+    <t>OISHI POPCRN COK 100</t>
+  </si>
+  <si>
+    <t>20125388</t>
+  </si>
+  <si>
+    <t>OISHI PCORN M/BLG100</t>
+  </si>
+  <si>
+    <t>20045784</t>
+  </si>
+  <si>
+    <t>OISHI SPNG/C CHO 100</t>
+  </si>
+  <si>
+    <t>20047335</t>
+  </si>
+  <si>
+    <t>OISHI SPNG STRW 100G</t>
+  </si>
+  <si>
+    <t>20136289</t>
+  </si>
+  <si>
+    <t>OISHI SPONGE UBI 100</t>
+  </si>
+  <si>
+    <t>20034686</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW UBI 100</t>
+  </si>
+  <si>
+    <t>20034685</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW CHO 100</t>
+  </si>
+  <si>
+    <t>20097777</t>
+  </si>
+  <si>
+    <t>KRISBEE PLW CHO 100G</t>
+  </si>
+  <si>
+    <t>20141746</t>
+  </si>
+  <si>
+    <t>OISHI PLLOW STRW 100</t>
+  </si>
+  <si>
+    <t>20036562</t>
+  </si>
+  <si>
+    <t>S/N SOSIS AYAM 500</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20129035</t>
+  </si>
+  <si>
+    <t>S/N SS AYM.BWG 2X40G</t>
+  </si>
+  <si>
+    <t>10024188</t>
+  </si>
+  <si>
+    <t>SOZZIS SOSIS AYAM 3S</t>
   </si>
   <si>
     <t>10024189</t>
@@ -1129,43 +1288,16 @@
     <t>SOZZIS SOSIS SAPI 3S</t>
   </si>
   <si>
-    <t>10024188</t>
-  </si>
-  <si>
-    <t>SOZZIS SOSIS AYAM 3S</t>
-  </si>
-  <si>
-    <t>20129035</t>
-  </si>
-  <si>
-    <t>S/N SS AYM.BWG 2X40G</t>
-  </si>
-  <si>
-    <t>20036562</t>
-  </si>
-  <si>
-    <t>S/N SOSIS AYAM 500</t>
-  </si>
-  <si>
-    <t>20138466</t>
-  </si>
-  <si>
-    <t>NABATI AHH STRW 30G</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20135812</t>
-  </si>
-  <si>
-    <t>NABATI RCHSE AHH 30G</t>
-  </si>
-  <si>
-    <t>20137069</t>
-  </si>
-  <si>
-    <t>KUSUKA UBI BBQ 42G</t>
+    <t>20028585</t>
+  </si>
+  <si>
+    <t>MI GEMEZ ENAK PREM22</t>
+  </si>
+  <si>
+    <t>20091447</t>
+  </si>
+  <si>
+    <t>MI GEMEZ SPICY 3X26G</t>
   </si>
   <si>
     <t>10027672</t>
@@ -1174,127 +1306,19 @@
     <t>GERY SNCK SEREAL 100</t>
   </si>
   <si>
-    <t>20091447</t>
-  </si>
-  <si>
-    <t>MI GEMEZ SPICY 3X26G</t>
-  </si>
-  <si>
-    <t>20028585</t>
-  </si>
-  <si>
-    <t>MI GEMEZ ENAK PREM22</t>
-  </si>
-  <si>
     <t>20103852</t>
   </si>
   <si>
     <t>JETZ CHOCOFIESTA 65G</t>
   </si>
   <si>
-    <t>20004229</t>
-  </si>
-  <si>
-    <t>SMAX RING CHEESE 40G</t>
-  </si>
-  <si>
-    <t>20081238</t>
-  </si>
-  <si>
-    <t>TARO NET TRYK BBQ 62</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20055205</t>
-  </si>
-  <si>
-    <t>TARO SEAWEED 62G</t>
-  </si>
-  <si>
-    <t>20055204</t>
-  </si>
-  <si>
-    <t>TARO POTATO BBQ 62G</t>
-  </si>
-  <si>
-    <t>10000753</t>
-  </si>
-  <si>
-    <t>TARO SNACK SEAWED 32</t>
-  </si>
-  <si>
-    <t>10000752</t>
-  </si>
-  <si>
-    <t>TARO SNACK BARBQ 32G</t>
-  </si>
-  <si>
-    <t>20069696</t>
-  </si>
-  <si>
-    <t>OISHI POPCRN KRML100</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20069844</t>
-  </si>
-  <si>
-    <t>OISHI POPCRN COK 100</t>
-  </si>
-  <si>
-    <t>20125388</t>
-  </si>
-  <si>
-    <t>OISHI PCORN M/BLG100</t>
-  </si>
-  <si>
-    <t>20045784</t>
-  </si>
-  <si>
-    <t>OISHI SPNG/C CHO 100</t>
-  </si>
-  <si>
-    <t>20047335</t>
-  </si>
-  <si>
-    <t>OISHI SPNG STRW 100G</t>
-  </si>
-  <si>
-    <t>20136289</t>
-  </si>
-  <si>
-    <t>OISHI SPONGE UBI 100</t>
-  </si>
-  <si>
-    <t>20034686</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW UBI 100</t>
-  </si>
-  <si>
-    <t>20034685</t>
-  </si>
-  <si>
-    <t>OISHI PILLOW CHO 100</t>
-  </si>
-  <si>
-    <t>20097777</t>
-  </si>
-  <si>
-    <t>KRISBEE PLW CHO 100G</t>
-  </si>
-  <si>
     <t>20007824</t>
   </si>
   <si>
     <t>D/K KCNG SANGRAI 180</t>
   </si>
   <si>
-    <t>32</t>
+    <t>33</t>
   </si>
   <si>
     <t>10000348</t>
@@ -1333,7 +1357,7 @@
     <t>DK KCNG BWNG PTH 180</t>
   </si>
   <si>
-    <t>33</t>
+    <t>34</t>
   </si>
   <si>
     <t>20040528</t>
@@ -1366,37 +1390,64 @@
     <t>GRUDA PILUS MI GR 80</t>
   </si>
   <si>
+    <t>10026501</t>
+  </si>
+  <si>
+    <t>DK KACANG SUKRO 95G</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20035264</t>
+  </si>
+  <si>
+    <t>IDM KC.ATOM/SHANG140</t>
+  </si>
+  <si>
+    <t>10029724</t>
+  </si>
+  <si>
+    <t>GARUDA KCNG ATOM 100</t>
+  </si>
+  <si>
+    <t>10003840</t>
+  </si>
+  <si>
+    <t>GARUDA KCG.TELUR 110</t>
+  </si>
+  <si>
+    <t>20072370</t>
+  </si>
+  <si>
+    <t>IDM KCNG BUMBU 150G</t>
+  </si>
+  <si>
+    <t>20042632</t>
+  </si>
+  <si>
+    <t>IDM KCG ATOM PDS 140</t>
+  </si>
+  <si>
+    <t>20136516</t>
+  </si>
+  <si>
+    <t>IDM KC ATM CB IJO120</t>
+  </si>
+  <si>
     <t>20072316</t>
   </si>
   <si>
     <t>D/K SUKRO KEDELE 95G</t>
   </si>
   <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20072370</t>
-  </si>
-  <si>
-    <t>IDM KCNG BUMBU 150G</t>
-  </si>
-  <si>
-    <t>10003840</t>
-  </si>
-  <si>
-    <t>GARUDA KCG.TELUR 110</t>
-  </si>
-  <si>
-    <t>20042632</t>
-  </si>
-  <si>
-    <t>IDM KCG ATOM PDS 140</t>
-  </si>
-  <si>
-    <t>20136516</t>
-  </si>
-  <si>
-    <t>IDM KC ATM CB IJO120</t>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20062966</t>
+  </si>
+  <si>
+    <t>DK SUKRO BBQ 95G</t>
   </si>
   <si>
     <t>20084707</t>
@@ -1405,31 +1456,28 @@
     <t>SUKRO KC OVEN BWG 95</t>
   </si>
   <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20062966</t>
-  </si>
-  <si>
-    <t>DK SUKRO BBQ 95G</t>
-  </si>
-  <si>
-    <t>20035264</t>
-  </si>
-  <si>
-    <t>IDM KC.ATOM/SHANG140</t>
-  </si>
-  <si>
-    <t>10029724</t>
-  </si>
-  <si>
-    <t>GARUDA KCNG ATOM 100</t>
-  </si>
-  <si>
-    <t>10026501</t>
-  </si>
-  <si>
-    <t>DK KACANG SUKRO 95G</t>
+    <t>20139132</t>
+  </si>
+  <si>
+    <t>GRUDA RS.MAX B&amp;S 80G</t>
+  </si>
+  <si>
+    <t>20120796</t>
+  </si>
+  <si>
+    <t>GRUDA ROSTA JG.B 95</t>
+  </si>
+  <si>
+    <t>20089490</t>
+  </si>
+  <si>
+    <t>GARUDA ROSTA PDS 90G</t>
+  </si>
+  <si>
+    <t>10005355</t>
+  </si>
+  <si>
+    <t>GRUDA K.ATOM PDS 220</t>
   </si>
   <si>
     <t>20056977</t>
@@ -1438,7 +1486,7 @@
     <t>GARUDA ROSTA BWG 95</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>20095753</t>
@@ -1447,37 +1495,16 @@
     <t>GRUDA ROSTA WGYU 95</t>
   </si>
   <si>
-    <t>20139132</t>
-  </si>
-  <si>
-    <t>GRUDA RS.MAX B&amp;S 80G</t>
-  </si>
-  <si>
-    <t>20120796</t>
-  </si>
-  <si>
-    <t>GRUDA ROSTA JG.B 95</t>
-  </si>
-  <si>
-    <t>20089490</t>
-  </si>
-  <si>
-    <t>GARUDA ROSTA PDS 90G</t>
-  </si>
-  <si>
-    <t>10005355</t>
-  </si>
-  <si>
-    <t>GRUDA K.ATOM PDS 220</t>
-  </si>
-  <si>
     <t>20137700</t>
   </si>
   <si>
     <t>MAYASI CSHW KTCY 35G</t>
   </si>
   <si>
-    <t>37</t>
+    <t>20066374</t>
+  </si>
+  <si>
+    <t>IDM MIX NUTS 80G</t>
   </si>
   <si>
     <t>20104000</t>
@@ -1492,79 +1519,73 @@
     <t>IDM KCNG KORO BLD 80</t>
   </si>
   <si>
+    <t>10003507</t>
+  </si>
+  <si>
+    <t>MR.P KACANG MADU 80G</t>
+  </si>
+  <si>
+    <t>20047037</t>
+  </si>
+  <si>
+    <t>IDM KACANG BALI 150G</t>
+  </si>
+  <si>
+    <t>20052766</t>
+  </si>
+  <si>
+    <t>IDM KCNG METE MDU 80</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20096682</t>
+  </si>
+  <si>
+    <t>IDM KACANG JUMBO 80</t>
+  </si>
+  <si>
+    <t>20112944</t>
+  </si>
+  <si>
+    <t>IDM KUACI SUSU 80G</t>
+  </si>
+  <si>
     <t>20093516</t>
   </si>
   <si>
     <t>INDOMARET KUACI 80G</t>
   </si>
   <si>
-    <t>20112944</t>
-  </si>
-  <si>
-    <t>IDM KUACI SUSU 80G</t>
-  </si>
-  <si>
-    <t>20066374</t>
-  </si>
-  <si>
-    <t>IDM MIX NUTS 80G</t>
-  </si>
-  <si>
-    <t>20052766</t>
-  </si>
-  <si>
-    <t>IDM KCNG METE MDU 80</t>
-  </si>
-  <si>
-    <t>10003507</t>
-  </si>
-  <si>
-    <t>MR.P KACANG MADU 80G</t>
-  </si>
-  <si>
-    <t>20096682</t>
-  </si>
-  <si>
-    <t>IDM KACANG JUMBO 80</t>
-  </si>
-  <si>
-    <t>20047037</t>
-  </si>
-  <si>
-    <t>IDM KACANG BALI 150G</t>
-  </si>
-  <si>
     <t>20098348</t>
   </si>
   <si>
-    <t>REBO KUACI ORIGNL140</t>
-  </si>
-  <si>
-    <t>38</t>
+    <t>REBO KUACI ORIGNL120</t>
   </si>
   <si>
     <t>20068536</t>
   </si>
   <si>
-    <t>REBO KUACI G.TEA 140</t>
+    <t>REBO KUACI G.TEA 120</t>
   </si>
   <si>
     <t>20093909</t>
   </si>
   <si>
-    <t>REBO KUACI MILK 140</t>
+    <t>REBO KUACI MILK 120</t>
   </si>
   <si>
     <t>20098334</t>
   </si>
   <si>
-    <t>REBO KUACI CRM 140G</t>
+    <t>REBO KUACI CRM 120G</t>
   </si>
   <si>
     <t>20130147</t>
   </si>
   <si>
-    <t>REBO KUACI CCNUT 140</t>
+    <t>REBO KUACI CCNUT 120</t>
   </si>
 </sst>
 </file>
@@ -1957,7 +1978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F236"/>
+  <dimension ref="A1:F239"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2304,7 +2325,7 @@
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2338,10 +2359,10 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -2361,7 +2382,7 @@
         <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -2381,7 +2402,7 @@
         <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -2401,7 +2422,7 @@
         <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -2421,7 +2442,7 @@
         <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -2438,10 +2459,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -2458,10 +2479,10 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -2481,7 +2502,7 @@
         <v>18</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -2501,7 +2522,7 @@
         <v>18</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -2521,7 +2542,7 @@
         <v>18</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -2541,7 +2562,7 @@
         <v>18</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -2558,13 +2579,13 @@
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2578,13 +2599,13 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2601,7 +2622,7 @@
         <v>22</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>37</v>
@@ -2621,7 +2642,7 @@
         <v>22</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>37</v>
@@ -2641,7 +2662,7 @@
         <v>22</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>37</v>
@@ -2661,7 +2682,7 @@
         <v>22</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>37</v>
@@ -2681,7 +2702,7 @@
         <v>22</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>37</v>
@@ -2689,10 +2710,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2701,7 +2722,7 @@
         <v>22</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>37</v>
@@ -2709,10 +2730,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2721,18 +2742,18 @@
         <v>22</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2741,18 +2762,18 @@
         <v>22</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2761,7 +2782,7 @@
         <v>22</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>37</v>
@@ -2769,19 +2790,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>37</v>
@@ -2789,19 +2810,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>37</v>
@@ -2809,19 +2830,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>37</v>
@@ -2829,39 +2850,39 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>37</v>
@@ -2869,19 +2890,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>37</v>
@@ -2889,19 +2910,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>22</v>
+        <v>82</v>
       </c>
       <c r="F47" s="1" t="s">
         <v>37</v>
@@ -2909,19 +2930,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>5</v>
@@ -2929,19 +2950,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>5</v>
@@ -2949,19 +2970,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>5</v>
@@ -2969,19 +2990,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2989,16 +3010,16 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>4</v>
@@ -3009,16 +3030,16 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>8</v>
@@ -3029,16 +3050,16 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>11</v>
@@ -3049,16 +3070,16 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>15</v>
@@ -3069,16 +3090,16 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>18</v>
@@ -3089,16 +3110,16 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>22</v>
@@ -3109,19 +3130,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -3129,16 +3150,16 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>4</v>
@@ -3149,16 +3170,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>8</v>
@@ -3169,56 +3190,56 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>18</v>
@@ -3229,16 +3250,16 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>22</v>
@@ -3249,19 +3270,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>5</v>
@@ -3269,16 +3290,16 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>4</v>
@@ -3289,56 +3310,56 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E67" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>15</v>
@@ -3349,16 +3370,16 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>18</v>
@@ -3369,16 +3390,16 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>4</v>
@@ -3389,16 +3410,16 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>8</v>
@@ -3409,16 +3430,16 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>11</v>
@@ -3429,16 +3450,16 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>15</v>
@@ -3449,16 +3470,16 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>159</v>
+        <v>95</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>18</v>
@@ -3469,16 +3490,16 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>4</v>
@@ -3489,39 +3510,39 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>19</v>
@@ -3529,42 +3550,42 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3578,50 +3599,50 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="E82" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -3629,39 +3650,39 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>12</v>
@@ -3678,10 +3699,10 @@
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>12</v>
@@ -3689,59 +3710,59 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B87" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="C87" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>37</v>
@@ -3749,19 +3770,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>37</v>
@@ -3769,19 +3790,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>37</v>
@@ -3798,10 +3819,10 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>37</v>
@@ -3809,19 +3830,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B93" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="C93" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="E93" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>37</v>
@@ -3829,36 +3850,36 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>18</v>
@@ -3869,16 +3890,16 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>22</v>
@@ -3889,16 +3910,16 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>4</v>
@@ -3909,16 +3930,16 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="C98" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>8</v>
@@ -3929,16 +3950,16 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>11</v>
@@ -3949,16 +3970,16 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>15</v>
@@ -3969,16 +3990,16 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>18</v>
@@ -3989,16 +4010,16 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>22</v>
@@ -4009,16 +4030,16 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>4</v>
@@ -4029,16 +4050,16 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="C104" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>229</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>8</v>
@@ -4049,16 +4070,16 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>11</v>
@@ -4069,16 +4090,16 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>15</v>
@@ -4089,16 +4110,16 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>18</v>
@@ -4109,56 +4130,56 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>241</v>
-      </c>
-      <c r="B109" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="C109" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>240</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>11</v>
@@ -4169,16 +4190,16 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>15</v>
@@ -4189,16 +4210,16 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>18</v>
@@ -4209,16 +4230,16 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>22</v>
@@ -4229,16 +4250,16 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>4</v>
@@ -4249,16 +4270,16 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="C115" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>8</v>
@@ -4269,16 +4290,16 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>11</v>
@@ -4289,16 +4310,16 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>15</v>
@@ -4309,16 +4330,16 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>18</v>
@@ -4329,16 +4350,16 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>4</v>
@@ -4349,16 +4370,16 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>8</v>
@@ -4369,16 +4390,16 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>11</v>
@@ -4389,16 +4410,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>15</v>
@@ -4409,22 +4430,22 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>273</v>
+        <v>37</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4438,27 +4459,27 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>4</v>
@@ -4469,16 +4490,16 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>279</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>8</v>
@@ -4489,16 +4510,16 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B127" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>11</v>
@@ -4509,139 +4530,139 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>5</v>
+        <v>276</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B131" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="C131" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>291</v>
-      </c>
       <c r="E131" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>37</v>
@@ -4649,19 +4670,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>37</v>
@@ -4669,19 +4690,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>37</v>
@@ -4689,19 +4710,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B137" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="C137" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>37</v>
@@ -4709,19 +4730,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>37</v>
@@ -4729,19 +4750,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>37</v>
@@ -4749,39 +4770,39 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B141" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>304</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>37</v>
@@ -4789,19 +4810,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>37</v>
@@ -4809,19 +4830,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>37</v>
@@ -4829,19 +4850,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>37</v>
@@ -4849,19 +4870,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>37</v>
@@ -4869,19 +4890,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B146" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>315</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>37</v>
@@ -4889,119 +4910,119 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B151" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>37</v>
@@ -5009,19 +5030,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>37</v>
@@ -5029,19 +5050,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>37</v>
@@ -5049,139 +5070,139 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>86</v>
+        <v>4</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B159" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C159" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="E159" s="1" t="s">
-        <v>89</v>
+        <v>8</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>19</v>
@@ -5189,19 +5210,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>19</v>
@@ -5209,59 +5230,59 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B165" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>364</v>
       </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>354</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>37</v>
@@ -5269,56 +5290,56 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>18</v>
@@ -5329,99 +5350,99 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C170" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>367</v>
-      </c>
       <c r="E170" s="1" t="s">
-        <v>86</v>
+        <v>8</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>37</v>
@@ -5429,19 +5450,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>19</v>
@@ -5449,99 +5470,99 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>386</v>
       </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>86</v>
+        <v>18</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>89</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>37</v>
@@ -5549,10 +5570,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>3</v>
@@ -5561,18 +5582,18 @@
         <v>397</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>3</v>
@@ -5581,18 +5602,18 @@
         <v>397</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>3</v>
@@ -5601,18 +5622,18 @@
         <v>397</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>3</v>
@@ -5621,18 +5642,18 @@
         <v>397</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>3</v>
@@ -5641,27 +5662,27 @@
         <v>397</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>37</v>
@@ -5669,19 +5690,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>37</v>
@@ -5689,39 +5710,39 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>88</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>15</v>
+        <v>92</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>37</v>
@@ -5729,119 +5750,119 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B190" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C190" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E190" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>37</v>
@@ -5849,19 +5870,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>37</v>
@@ -5869,59 +5890,59 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>11</v>
+        <v>85</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B198" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="C198" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>427</v>
-      </c>
       <c r="E198" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>37</v>
@@ -5929,19 +5950,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>37</v>
@@ -5949,39 +5970,39 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>37</v>
@@ -5989,19 +6010,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>37</v>
@@ -6009,19 +6030,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F203" s="1" t="s">
         <v>37</v>
@@ -6029,19 +6050,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B204" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="C204" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>440</v>
-      </c>
       <c r="E204" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>37</v>
@@ -6049,19 +6070,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>37</v>
@@ -6069,19 +6090,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>37</v>
@@ -6089,19 +6110,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F207" s="1" t="s">
         <v>37</v>
@@ -6109,19 +6130,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>37</v>
@@ -6129,19 +6150,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>37</v>
@@ -6149,19 +6170,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B210" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D210" s="1" t="s">
         <v>461</v>
       </c>
-      <c r="C210" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D210" s="1" t="s">
-        <v>453</v>
-      </c>
       <c r="E210" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>37</v>
@@ -6169,19 +6190,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>37</v>
@@ -6189,19 +6210,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>37</v>
@@ -6209,19 +6230,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B213" s="1" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>37</v>
@@ -6229,19 +6250,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>37</v>
@@ -6249,19 +6270,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>18</v>
+        <v>82</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>37</v>
@@ -6269,16 +6290,16 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E216" s="1" t="s">
         <v>4</v>
@@ -6289,16 +6310,16 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D217" s="1" t="s">
         <v>476</v>
-      </c>
-      <c r="B217" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D217" s="1" t="s">
-        <v>475</v>
       </c>
       <c r="E217" s="1" t="s">
         <v>8</v>
@@ -6309,16 +6330,16 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E218" s="1" t="s">
         <v>11</v>
@@ -6329,16 +6350,16 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E219" s="1" t="s">
         <v>15</v>
@@ -6349,16 +6370,16 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E220" s="1" t="s">
         <v>18</v>
@@ -6369,16 +6390,16 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>22</v>
@@ -6389,19 +6410,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>4</v>
+        <v>82</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>37</v>
@@ -6418,130 +6439,130 @@
         <v>3</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D224" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B224" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="C224" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>488</v>
-      </c>
       <c r="E224" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>90</v>
+        <v>37</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F229" s="1" t="s">
         <v>19</v>
@@ -6549,119 +6570,119 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>488</v>
+        <v>508</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B232" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" s="1" t="s">
         <v>508</v>
       </c>
-      <c r="C232" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D232" s="1" t="s">
-        <v>509</v>
-      </c>
       <c r="E232" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>37</v>
@@ -6669,21 +6690,81 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F236" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F239" s="1" t="s">
         <v>37</v>
       </c>
     </row>
